--- a/smoment/autopacmen_output/Mitocore_Preliminary/Mitocore_Preliminary_kcats_calibrated.xlsx
+++ b/smoment/autopacmen_output/Mitocore_Preliminary/Mitocore_Preliminary_kcats_calibrated.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>original_kcats</t>
   </si>
@@ -25,46 +25,52 @@
     <t>original_reactions</t>
   </si>
   <si>
+    <t>LDH_L_reverse</t>
+  </si>
+  <si>
     <t>CV_MitoCore_forward</t>
   </si>
   <si>
+    <t>CIII_MitoCore_forward</t>
+  </si>
+  <si>
     <t>CI_MitoCore_forward</t>
   </si>
   <si>
+    <t>ACONTm_forward</t>
+  </si>
+  <si>
+    <t>SUCOASm_reverse</t>
+  </si>
+  <si>
+    <t>r0178_forward</t>
+  </si>
+  <si>
+    <t>r0178_reverse</t>
+  </si>
+  <si>
+    <t>ICDHxm_forward</t>
+  </si>
+  <si>
+    <t>ICDHxm_reverse</t>
+  </si>
+  <si>
+    <t>AACTOORm_MitoCore_forward</t>
+  </si>
+  <si>
+    <t>AACTOORm_MitoCore_reverse</t>
+  </si>
+  <si>
+    <t>CIV_MitoCore_forward</t>
+  </si>
+  <si>
+    <t>CIV_MitoCore_reverse</t>
+  </si>
+  <si>
     <t>PDHm_forward</t>
   </si>
   <si>
     <t>PDHm_reverse</t>
-  </si>
-  <si>
-    <t>ACONTm_forward</t>
-  </si>
-  <si>
-    <t>ACONT_forward</t>
-  </si>
-  <si>
-    <t>SUCOASm_reverse</t>
-  </si>
-  <si>
-    <t>GHMT2r_forward</t>
-  </si>
-  <si>
-    <t>MCOATA_forward</t>
-  </si>
-  <si>
-    <t>CIII_MitoCore_forward</t>
-  </si>
-  <si>
-    <t>CIV_MitoCore_forward</t>
-  </si>
-  <si>
-    <t>CIV_MitoCore_reverse</t>
-  </si>
-  <si>
-    <t>ICDHxm_forward</t>
-  </si>
-  <si>
-    <t>ICDHxm_reverse</t>
   </si>
 </sst>
 </file>
@@ -422,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -441,10 +447,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>18.5</v>
+        <v>0.92</v>
       </c>
       <c r="C2">
-        <v>340.2551856147404</v>
+        <v>46.71967872985251</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -452,10 +458,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>18.5</v>
       </c>
       <c r="C3">
-        <v>3167.110672939455</v>
+        <v>919.0611018502041</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -463,10 +469,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>2.4</v>
+        <v>15.04</v>
       </c>
       <c r="C4">
-        <v>93.80603612837179</v>
+        <v>233.9758641226612</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -474,10 +480,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>2.4</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>93.80603612837179</v>
+        <v>2659.306458797353</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -488,7 +494,7 @@
         <v>5.2</v>
       </c>
       <c r="C6">
-        <v>261.4122506890268</v>
+        <v>264.0677508702277</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -496,10 +502,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>5.2</v>
+        <v>19.8</v>
       </c>
       <c r="C7">
-        <v>261.4122518428364</v>
+        <v>1005.488933908162</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -507,10 +513,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>19.8</v>
+        <v>27.15</v>
       </c>
       <c r="C8">
-        <v>995.3770709328303</v>
+        <v>1378.738174354132</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -518,10 +524,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>0.57</v>
+        <v>27.15</v>
       </c>
       <c r="C9">
-        <v>28.65480403310118</v>
+        <v>1378.738174354132</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -529,10 +535,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>30.625</v>
       </c>
       <c r="C10">
-        <v>603.2590425163336</v>
+        <v>1555.20657601392</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -540,10 +546,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>79</v>
+        <v>21.3</v>
       </c>
       <c r="C11">
-        <v>3971.454023899369</v>
+        <v>1081.662043072539</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -551,10 +557,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>38.1</v>
+        <v>0.67</v>
       </c>
       <c r="C12">
-        <v>1915.347441291009</v>
+        <v>34.02410946022999</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -562,10 +568,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>13.33333</v>
+        <v>0.67</v>
       </c>
       <c r="C13">
-        <v>670.2876509025891</v>
+        <v>34.02410946022999</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -573,10 +579,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>20.5</v>
+        <v>37.4</v>
       </c>
       <c r="C14">
-        <v>1030.567526930957</v>
+        <v>1899.2560824312</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -584,10 +590,32 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>81.685</v>
+        <v>38.85</v>
       </c>
       <c r="C15">
-        <v>4106.434557919766</v>
+        <v>1972.890342311554</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>98</v>
+      </c>
+      <c r="C16">
+        <v>4976.661671234794</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>0.48</v>
+      </c>
+      <c r="C17">
+        <v>24.37548573666022</v>
       </c>
     </row>
   </sheetData>
